--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_0_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_0_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>438334.5809165197</v>
+        <v>438336.2585840487</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446352025</v>
+        <v>925399.3994514374</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422528</v>
+        <v>18327015.93006068</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5667826.649228099</v>
+        <v>5667942.033436031</v>
       </c>
     </row>
     <row r="11">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>112.3289263072337</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>149.8691179411497</v>
@@ -703,7 +703,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>102.2970636939287</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V3" t="n">
-        <v>232.8005871494253</v>
+        <v>147.2379120664689</v>
       </c>
       <c r="W3" t="n">
-        <v>4.525096818297269</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -825,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>22.26949182588285</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>22.0339917726843</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -901,13 +901,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>230.8744955960827</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -928,31 +928,31 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>102.2970636939287</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="6">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84.91820125737712</v>
+        <v>84.97365353379637</v>
       </c>
       <c r="C6" t="n">
         <v>172.7084989883157</v>
@@ -1062,10 +1062,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>39.82778746869526</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>120.9273370453295</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
         <v>11.94928935461252</v>
@@ -1177,10 +1177,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>90.34777433931619</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1202,28 +1202,28 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>84.97365353379641</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1247,22 +1247,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>4.525096818297269</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1366,19 +1366,19 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1402,22 +1402,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75.18232784062694</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
         <v>147.4450655646388</v>
@@ -1454,10 +1454,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>84.97365353379641</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -1484,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>110.9174757594852</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1615,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>11.19305615617957</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1642,22 +1642,22 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>70.98780391928699</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1676,28 +1676,28 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>84.97365353379641</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1724,19 +1724,19 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>104.6829309709404</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1843,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>90.38893773807641</v>
       </c>
       <c r="J17" t="n">
-        <v>1.79691042959408</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1876,19 +1876,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1919,22 +1919,22 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,25 +1958,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>20.99531631735417</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>104.7383832473596</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S19" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.79691042959408</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>210.4758895704059</v>
+        <v>84.41978777916125</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2113,13 +2113,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>145.3912560091964</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>22.03399177268427</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2317,16 +2317,16 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2371,10 +2371,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2396,10 +2396,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>10.97611376273713</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>74.18006676291769</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -2478,61 +2478,61 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>220.8837963815378</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2605,13 +2605,13 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2678,13 +2678,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>160.5527731999126</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>4.580549094716531</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.809496073036188</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2836,19 +2836,19 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>202.2821007854552</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="30">
@@ -2909,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>63.847659665762</v>
+        <v>65.1306020652372</v>
       </c>
       <c r="U30" t="n">
         <v>225.9413820809748</v>
@@ -2921,13 +2921,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2979,13 +2979,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>44.30348359856706</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>52.42556848774763</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3061,22 +3061,22 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>94.3836124726555</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="33">
@@ -3143,25 +3143,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>162.4005985629045</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>89.66547645067541</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>241</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="C35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3268,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="36">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>29.84813499229551</v>
+        <v>115.5785074418532</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3389,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -3465,16 +3465,16 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3499,16 +3499,16 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>220.2131257424249</v>
       </c>
       <c r="F38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3544,19 +3544,19 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3575,22 +3575,22 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>51.83632157383516</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0.7465913262578567</v>
@@ -3620,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>81.94696239689884</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -3736,19 +3736,19 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>241</v>
+        <v>51.72215467797748</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3772,25 +3772,25 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3809,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>59.0643807471702</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3854,28 +3854,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>50.01653186979276</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3964,22 +3964,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4027,13 +4027,13 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>220.1862512213237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4046,13 +4046,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C45" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4061,10 +4061,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>68.37747039897646</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>30.51007763073408</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y45" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4122,76 +4122,76 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R2" t="n">
-        <v>802.5254372164702</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S2" t="n">
-        <v>591.3940537960203</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T2" t="n">
-        <v>366.0447108019482</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="U2" t="n">
-        <v>122.6103673676048</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="V2" t="n">
-        <v>122.6103673676048</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="W2" t="n">
-        <v>122.6103673676048</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="X2" t="n">
-        <v>19.28</v>
+        <v>132.7447050367114</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.28</v>
+        <v>132.7447050367114</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="C3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="D3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="E3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="F3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="G3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="H3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L3" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M3" t="n">
-        <v>613.1906659261865</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N3" t="n">
-        <v>613.1906659261865</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="O3" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S3" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T3" t="n">
-        <v>487.2265313623206</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U3" t="n">
-        <v>259.0029130987097</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V3" t="n">
-        <v>23.85080486696694</v>
+        <v>110.334904905842</v>
       </c>
       <c r="W3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="X3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="C4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="D4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="E4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="F4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="G4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="H4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="I4" t="n">
-        <v>136.0766383258138</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="J4" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q4" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="S4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="T4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="U4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="V4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="W4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="X4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="Y4" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C5" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D5" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E5" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F5" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G5" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="H5" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T5" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U5" t="n">
-        <v>122.6103673676048</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V5" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W5" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X5" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>878.2240391339625</v>
+        <v>878.2251822441752</v>
       </c>
       <c r="C6" t="n">
-        <v>703.7710098528355</v>
+        <v>703.7721529630483</v>
       </c>
       <c r="D6" t="n">
-        <v>554.8366001915842</v>
+        <v>554.837743301797</v>
       </c>
       <c r="E6" t="n">
-        <v>395.5991451861288</v>
+        <v>395.6002882963414</v>
       </c>
       <c r="F6" t="n">
-        <v>249.0645872130137</v>
+        <v>249.0657303232264</v>
       </c>
       <c r="G6" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="H6" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L6" t="n">
-        <v>248.2299999999999</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M6" t="n">
-        <v>486.8199999999999</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N6" t="n">
-        <v>725.41</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="O6" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P6" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I7" t="n">
-        <v>19.28</v>
+        <v>113.583345248266</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="C8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="D8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="E8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="F8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="G8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="H8" t="n">
-        <v>31.34998924708335</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I8" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R8" t="n">
-        <v>802.5254372164702</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S8" t="n">
-        <v>591.3940537960203</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T8" t="n">
-        <v>366.0447108019482</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U8" t="n">
-        <v>122.6103673676048</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="V8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="W8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="X8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="Y8" t="n">
-        <v>31.34998924708335</v>
+        <v>366.1018663125844</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C9" t="n">
-        <v>19.28</v>
+        <v>789.6041262295092</v>
       </c>
       <c r="D9" t="n">
-        <v>19.28</v>
+        <v>640.669716568258</v>
       </c>
       <c r="E9" t="n">
-        <v>19.28</v>
+        <v>481.4322615628025</v>
       </c>
       <c r="F9" t="n">
-        <v>19.28</v>
+        <v>334.8977035896875</v>
       </c>
       <c r="G9" t="n">
-        <v>19.28</v>
+        <v>196.166878172303</v>
       </c>
       <c r="H9" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I9" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L9" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M9" t="n">
-        <v>374.6006659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N9" t="n">
-        <v>613.1906659261865</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O9" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P9" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S9" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T9" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U9" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V9" t="n">
-        <v>23.85080486696694</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W9" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X9" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I10" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C11" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D11" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E11" t="n">
-        <v>962.184938960006</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F11" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G11" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H11" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R11" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S11" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T11" t="n">
-        <v>964</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U11" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V11" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W11" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X11" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y11" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C12" t="n">
-        <v>613.471380709992</v>
+        <v>789.6041262295092</v>
       </c>
       <c r="D12" t="n">
-        <v>464.5369710487408</v>
+        <v>640.669716568258</v>
       </c>
       <c r="E12" t="n">
-        <v>305.2995160432853</v>
+        <v>481.4322615628025</v>
       </c>
       <c r="F12" t="n">
-        <v>158.7649580701702</v>
+        <v>334.8977035896875</v>
       </c>
       <c r="G12" t="n">
-        <v>20.03413265278571</v>
+        <v>196.166878172303</v>
       </c>
       <c r="H12" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I12" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M12" t="n">
-        <v>304.1765223866491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N12" t="n">
-        <v>542.7665223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O12" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="C14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="D14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="E14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="F14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="G14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="H14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="I14" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R14" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S14" t="n">
-        <v>802.5254372164702</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="T14" t="n">
-        <v>730.820584772746</v>
+        <v>517.4848137278872</v>
       </c>
       <c r="U14" t="n">
-        <v>487.3862413384025</v>
+        <v>274.0360370837871</v>
       </c>
       <c r="V14" t="n">
-        <v>243.9518979040591</v>
+        <v>274.0360370837871</v>
       </c>
       <c r="W14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="X14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="Y14" t="n">
-        <v>243.9518979040591</v>
+        <v>30.58726043968704</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C15" t="n">
-        <v>19.28</v>
+        <v>789.6041262295092</v>
       </c>
       <c r="D15" t="n">
-        <v>19.28</v>
+        <v>640.669716568258</v>
       </c>
       <c r="E15" t="n">
-        <v>19.28</v>
+        <v>481.4322615628025</v>
       </c>
       <c r="F15" t="n">
-        <v>19.28</v>
+        <v>334.8977035896875</v>
       </c>
       <c r="G15" t="n">
-        <v>19.28</v>
+        <v>196.166878172303</v>
       </c>
       <c r="H15" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I15" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L15" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M15" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N15" t="n">
-        <v>613.1906659261865</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O15" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P15" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T15" t="n">
-        <v>588.3960608094349</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U15" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V15" t="n">
-        <v>125.0203343140812</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W15" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X15" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y15" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I16" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="C17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="D17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="E17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="F17" t="n">
-        <v>720.5656565656566</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="G17" t="n">
-        <v>477.1313131313132</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="H17" t="n">
-        <v>233.6969696969697</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="I17" t="n">
-        <v>21.09506103999402</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R17" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S17" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T17" t="n">
-        <v>964</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="W17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="X17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="Y17" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>668.2057357840049</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C18" t="n">
-        <v>668.2057357840049</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D18" t="n">
-        <v>668.2057357840049</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E18" t="n">
-        <v>508.9682807785495</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F18" t="n">
-        <v>362.4337228054344</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G18" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H18" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L18" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M18" t="n">
-        <v>487.8331058683492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N18" t="n">
-        <v>711.9619638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O18" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P18" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S18" t="n">
-        <v>689.4131260035546</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T18" t="n">
-        <v>668.2057357840049</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U18" t="n">
-        <v>668.2057357840049</v>
+        <v>360.2295980564601</v>
       </c>
       <c r="V18" t="n">
-        <v>668.2057357840049</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="W18" t="n">
-        <v>668.2057357840049</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="X18" t="n">
-        <v>668.2057357840049</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y18" t="n">
-        <v>668.2057357840049</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>964</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="C20" t="n">
-        <v>964</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="D20" t="n">
-        <v>720.5656565656566</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="E20" t="n">
-        <v>720.5656565656566</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="F20" t="n">
-        <v>718.7505955256626</v>
+        <v>104.5536560184564</v>
       </c>
       <c r="G20" t="n">
-        <v>475.3162520913191</v>
+        <v>104.5536560184564</v>
       </c>
       <c r="H20" t="n">
-        <v>231.8819086569757</v>
+        <v>104.5536560184564</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="X20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="Y20" t="n">
-        <v>964</v>
+        <v>348.0024326625565</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C21" t="n">
-        <v>817.1401454452562</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D21" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E21" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F21" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G21" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H21" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>304.1765223866491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>304.1765223866491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="F23" t="n">
-        <v>506.1486868686869</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="G23" t="n">
-        <v>262.7143434343434</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X23" t="n">
-        <v>953.9083846317729</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="C24" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>234.7819638733197</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M24" t="n">
-        <v>473.3719638733197</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>678.3261424048302</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>678.3261424048302</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V24" t="n">
-        <v>678.3261424048302</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W24" t="n">
-        <v>434.8917989704868</v>
+        <v>889.1277951440527</v>
       </c>
       <c r="X24" t="n">
-        <v>227.0402987649539</v>
+        <v>681.2762949385199</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.28</v>
+        <v>473.515996173566</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T26" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U26" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V26" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W26" t="n">
-        <v>506.1486868686869</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X26" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y26" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>325.0520129785705</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C27" t="n">
-        <v>325.0520129785705</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D27" t="n">
-        <v>325.0520129785705</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E27" t="n">
-        <v>165.814557973115</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>19.28</v>
+        <v>234.810827406191</v>
       </c>
       <c r="M27" t="n">
-        <v>257.87</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N27" t="n">
-        <v>496.46</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>735.0500000000001</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>917.693477613351</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T27" t="n">
-        <v>487.2265313623206</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U27" t="n">
-        <v>325.0520129785705</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V27" t="n">
-        <v>325.0520129785705</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W27" t="n">
-        <v>325.0520129785705</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X27" t="n">
-        <v>325.0520129785705</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y27" t="n">
-        <v>325.0520129785705</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>710.4740411974295</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>710.4740411974295</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W29" t="n">
-        <v>710.4740411974295</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X29" t="n">
-        <v>467.0396977630861</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y29" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M30" t="n">
-        <v>613.1906659261865</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N30" t="n">
-        <v>781.3565223866492</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>726.0900699296972</v>
+        <v>898.2686685760532</v>
       </c>
       <c r="U30" t="n">
-        <v>497.8664516660862</v>
+        <v>670.0450503124422</v>
       </c>
       <c r="V30" t="n">
-        <v>262.7143434343434</v>
+        <v>434.8929420806995</v>
       </c>
       <c r="W30" t="n">
-        <v>19.28</v>
+        <v>434.8929420806995</v>
       </c>
       <c r="X30" t="n">
-        <v>19.28</v>
+        <v>227.0414418751666</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>961.2510699645388</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>874.2187030436354</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C32" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D32" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E32" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964.0000000000512</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964.0000000000512</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>812.6170525847484</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S32" t="n">
-        <v>601.4856691642985</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T32" t="n">
-        <v>601.4856691642985</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U32" t="n">
-        <v>506.1486868686869</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V32" t="n">
-        <v>262.7143434343434</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="W32" t="n">
-        <v>262.7143434343434</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="X32" t="n">
-        <v>262.7143434343434</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="Y32" t="n">
-        <v>262.7143434343434</v>
+        <v>559.1338160830064</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M33" t="n">
-        <v>542.7665223866492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N33" t="n">
-        <v>542.7665223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>862.8304705528857</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T33" t="n">
-        <v>698.7894619034872</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U33" t="n">
-        <v>470.5658436398763</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="V33" t="n">
-        <v>470.5658436398763</v>
+        <v>353.3011080883284</v>
       </c>
       <c r="W33" t="n">
-        <v>227.1315002055328</v>
+        <v>109.8523314442283</v>
       </c>
       <c r="X33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C35" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D35" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E35" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F35" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G35" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R35" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S35" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T35" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U35" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V35" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W35" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X35" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y35" t="n">
-        <v>749.5830303030303</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>49.42963130534901</v>
+        <v>136.7812428759814</v>
       </c>
       <c r="C36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M36" t="n">
-        <v>486.8199999999999</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N36" t="n">
-        <v>725.41</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O36" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U36" t="n">
-        <v>735.7763817363891</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V36" t="n">
-        <v>500.6242735046464</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W36" t="n">
-        <v>257.1899300703029</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X36" t="n">
-        <v>257.1899300703029</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y36" t="n">
-        <v>49.42963130534901</v>
+        <v>304.9965798960495</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>262.7143434343434</v>
+        <v>485.167420504237</v>
       </c>
       <c r="C38" t="n">
-        <v>262.7143434343434</v>
+        <v>485.167420504237</v>
       </c>
       <c r="D38" t="n">
-        <v>262.7143434343434</v>
+        <v>485.167420504237</v>
       </c>
       <c r="E38" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F38" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G38" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S38" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T38" t="n">
-        <v>964</v>
+        <v>728.6161971483371</v>
       </c>
       <c r="U38" t="n">
-        <v>749.5830303030303</v>
+        <v>485.167420504237</v>
       </c>
       <c r="V38" t="n">
-        <v>506.1486868686869</v>
+        <v>485.167420504237</v>
       </c>
       <c r="W38" t="n">
-        <v>506.1486868686869</v>
+        <v>485.167420504237</v>
       </c>
       <c r="X38" t="n">
-        <v>262.7143434343434</v>
+        <v>485.167420504237</v>
       </c>
       <c r="Y38" t="n">
-        <v>262.7143434343434</v>
+        <v>485.167420504237</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>720.5656565656566</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C39" t="n">
-        <v>720.5656565656566</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D39" t="n">
-        <v>668.2057357840049</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E39" t="n">
-        <v>508.9682807785495</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F39" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G39" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H39" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I39" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M39" t="n">
-        <v>257.87</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N39" t="n">
-        <v>496.46</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O39" t="n">
-        <v>735.0500000000001</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P39" t="n">
-        <v>917.693477613351</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>964</v>
+        <v>881.2824460188192</v>
       </c>
       <c r="T39" t="n">
-        <v>964</v>
+        <v>679.0958513775852</v>
       </c>
       <c r="U39" t="n">
-        <v>964</v>
+        <v>679.0958513775852</v>
       </c>
       <c r="V39" t="n">
-        <v>964</v>
+        <v>679.0958513775852</v>
       </c>
       <c r="W39" t="n">
-        <v>720.5656565656566</v>
+        <v>435.6470747334852</v>
       </c>
       <c r="X39" t="n">
-        <v>720.5656565656566</v>
+        <v>227.7955745279523</v>
       </c>
       <c r="Y39" t="n">
-        <v>720.5656565656566</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T40" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U40" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V40" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>506.1486868686869</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="C41" t="n">
-        <v>506.1486868686869</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="D41" t="n">
-        <v>506.1486868686869</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="E41" t="n">
-        <v>262.7143434343434</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="F41" t="n">
-        <v>262.7143434343434</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="G41" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="H41" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S41" t="n">
-        <v>953.9083846317729</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T41" t="n">
-        <v>953.9083846317729</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U41" t="n">
-        <v>710.4740411974295</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="V41" t="n">
-        <v>710.4740411974295</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="W41" t="n">
-        <v>506.1486868686869</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="X41" t="n">
-        <v>506.1486868686869</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="Y41" t="n">
-        <v>506.1486868686869</v>
+        <v>284.1276524520142</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.28</v>
+        <v>253.395163045047</v>
       </c>
       <c r="C42" t="n">
-        <v>19.28</v>
+        <v>78.94213376392</v>
       </c>
       <c r="D42" t="n">
-        <v>19.28</v>
+        <v>78.94213376392</v>
       </c>
       <c r="E42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L42" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M42" t="n">
-        <v>487.8331058683492</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N42" t="n">
-        <v>726.4231058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O42" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T42" t="n">
-        <v>913.478250636573</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U42" t="n">
-        <v>913.478250636573</v>
+        <v>461.2466632505798</v>
       </c>
       <c r="V42" t="n">
-        <v>678.3261424048302</v>
+        <v>461.2466632505798</v>
       </c>
       <c r="W42" t="n">
-        <v>434.8917989704868</v>
+        <v>461.2466632505798</v>
       </c>
       <c r="X42" t="n">
-        <v>227.0402987649539</v>
+        <v>253.395163045047</v>
       </c>
       <c r="Y42" t="n">
-        <v>19.28</v>
+        <v>253.395163045047</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C44" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D44" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E44" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F44" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T44" t="n">
-        <v>728.5590416377008</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U44" t="n">
-        <v>728.5590416377008</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V44" t="n">
-        <v>728.5590416377008</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W44" t="n">
-        <v>728.5590416377008</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X44" t="n">
-        <v>728.5590416377008</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y44" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>456.036574534799</v>
+        <v>417.752636919763</v>
       </c>
       <c r="C45" t="n">
-        <v>281.583545253672</v>
+        <v>417.752636919763</v>
       </c>
       <c r="D45" t="n">
-        <v>132.6491355924207</v>
+        <v>268.8182272585117</v>
       </c>
       <c r="E45" t="n">
-        <v>132.6491355924207</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="F45" t="n">
-        <v>132.6491355924207</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="G45" t="n">
-        <v>132.6491355924207</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="H45" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L45" t="n">
-        <v>249.2431058683491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M45" t="n">
-        <v>486.8199999999999</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N45" t="n">
-        <v>725.41</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O45" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V45" t="n">
-        <v>862.8304705528857</v>
+        <v>793.8194741453639</v>
       </c>
       <c r="W45" t="n">
-        <v>862.8304705528857</v>
+        <v>793.8194741453639</v>
       </c>
       <c r="X45" t="n">
-        <v>832.012210319821</v>
+        <v>585.967973939831</v>
       </c>
       <c r="Y45" t="n">
-        <v>624.2519115548671</v>
+        <v>585.967973939831</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
   </sheetData>
@@ -7959,7 +7959,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L2" t="n">
         <v>417.6612145504504</v>
@@ -8038,19 +8038,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K3" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L3" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M3" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N3" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O3" t="n">
-        <v>242.3652322698316</v>
+        <v>369.031319612638</v>
       </c>
       <c r="P3" t="n">
         <v>318.4627686399372</v>
@@ -8202,7 +8202,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M5" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N5" t="n">
         <v>437.3469244119842</v>
@@ -8275,25 +8275,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
-        <v>243.1932080042808</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M6" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>383.5962444444444</v>
+        <v>369.031319612638</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8439,7 +8439,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M8" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N8" t="n">
         <v>437.3469244119842</v>
@@ -8518,19 +8518,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M9" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N9" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O9" t="n">
-        <v>242.3652322698316</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P9" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8685,7 +8685,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P11" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,22 +8749,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L12" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P12" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
         <v>139.9817740860215</v>
@@ -8907,7 +8907,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L14" t="n">
         <v>417.6612145504504</v>
@@ -8992,19 +8992,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
-        <v>131.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O15" t="n">
-        <v>242.3652322698316</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q15" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9150,7 +9150,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M17" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N17" t="n">
         <v>437.3469244119842</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L18" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M18" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N18" t="n">
-        <v>357.73449794694</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P18" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q18" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9463,22 +9463,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
-        <v>299.7048467786739</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>318.4627686399372</v>
+        <v>177.2597568922521</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,19 +9697,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
-        <v>356.2331311670658</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>233.2169876979182</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>229.6373335557741</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>186.7560391230408</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,7 +10329,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>321.7421299892884</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10414,19 +10414,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>177.2597568922521</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,10 +10566,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L35" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
         <v>449.5135334928325</v>
@@ -10645,22 +10645,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>255.4868966228399</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>372.3417120833333</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -10803,7 +10803,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
@@ -10818,7 +10818,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10888,19 +10888,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>186.7560391230408</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,7 +11040,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
@@ -11119,22 +11119,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>372.3417120833333</v>
+        <v>301.248502863135</v>
       </c>
       <c r="O42" t="n">
-        <v>382.5729051834858</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
         <v>139.9817740860215</v>
@@ -11292,7 +11292,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P44" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q44" t="n">
         <v>212.3149906599047</v>
@@ -11356,22 +11356,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L45" t="n">
-        <v>370.8403453034592</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M45" t="n">
-        <v>382.1106946610595</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N45" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P45" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q45" t="n">
         <v>139.9817740860215</v>
@@ -22504,7 +22504,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>382.7338416634806</v>
+        <v>270.4049153562469</v>
       </c>
       <c r="C2" t="n">
         <v>365.2728917710076</v>
@@ -22549,7 +22549,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -22561,7 +22561,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
         <v>327.7522584701349</v>
@@ -22570,7 +22570,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X2" t="n">
-        <v>267.4340369845403</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y2" t="n">
         <v>386.2379386560536</v>
@@ -22604,10 +22604,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -22643,10 +22643,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>85.56267508295639</v>
       </c>
       <c r="W3" t="n">
-        <v>247.1698863426223</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X3" t="n">
         <v>205.7729852034775</v>
@@ -22683,10 +22683,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -22704,13 +22704,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>177.2933913771695</v>
+        <v>155.2593996044852</v>
       </c>
       <c r="S4" t="n">
         <v>224.0165980369723</v>
@@ -22759,13 +22759,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H5" t="n">
-        <v>339.4748021157671</v>
+        <v>108.6003065196844</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22786,31 +22786,31 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V5" t="n">
-        <v>225.4551947762062</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W5" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X5" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="6">
@@ -22820,7 +22820,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.61498239249021</v>
+        <v>81.55953011607097</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -22920,10 +22920,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
-        <v>155.4504749272583</v>
+        <v>115.622687458563</v>
       </c>
       <c r="J7" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>22.26949182588285</v>
@@ -22941,13 +22941,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
         <v>224.0165980369723</v>
@@ -22996,10 +22996,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>218.5474650704376</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23035,10 +23035,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>237.4044841308187</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
         <v>349.240968717413</v>
@@ -23060,28 +23060,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2354442364965</v>
+        <v>27.26179070270005</v>
       </c>
       <c r="I9" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,22 +23105,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>247.1698863426223</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
@@ -23157,13 +23157,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,13 +23178,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23224,19 +23224,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>380.1334596426677</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23260,22 +23260,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V11" t="n">
-        <v>327.7522584701349</v>
+        <v>225.414031377446</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23297,7 +23297,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>97.52617114768879</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -23312,10 +23312,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>112.2354442364965</v>
+        <v>27.26179070270005</v>
       </c>
       <c r="I12" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,10 +23342,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
         <v>200.1647286948216</v>
@@ -23400,7 +23400,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>113.0991222774871</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T13" t="n">
         <v>227.9455894282815</v>
@@ -23473,10 +23473,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>199.2828334142263</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23500,22 +23500,22 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>152.1080456448444</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V14" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X14" t="n">
         <v>369.731100678469</v>
@@ -23534,28 +23534,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>112.2354442364965</v>
+        <v>27.26179070270005</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23582,19 +23582,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
-        <v>147.0120521899792</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X15" t="n">
         <v>205.7729852034775</v>
@@ -23631,13 +23631,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,13 +23652,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S16" t="n">
         <v>224.0165980369723</v>
@@ -23701,19 +23701,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>120.0869518323295</v>
       </c>
       <c r="J17" t="n">
-        <v>10.15237892501844</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23777,22 +23777,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,25 +23816,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>179.1694123774674</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>205.7729852034775</v>
+        <v>101.0346019561178</v>
       </c>
       <c r="Y18" t="n">
         <v>205.6826957773044</v>
@@ -23892,13 +23892,13 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S19" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
@@ -23932,22 +23932,22 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>405.0791353121173</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>126.0561017912447</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -23971,13 +23971,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
@@ -23995,7 +23995,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24008,7 +24008,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>27.31724297911936</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C22" t="n">
         <v>167.2468210986278</v>
@@ -24108,10 +24108,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J22" t="n">
-        <v>71.32518834398851</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24126,10 +24126,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
         <v>177.2933913771695</v>
@@ -24175,16 +24175,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>405.0665496686753</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24208,7 +24208,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
@@ -24229,10 +24229,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
-        <v>183.9558378705984</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24242,7 +24242,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>172.7084989883157</v>
@@ -24254,10 +24254,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24266,7 +24266,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,13 +24290,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>189.1886149320845</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -24305,7 +24305,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>177.5149163980019</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -24336,7 +24336,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>34.80401177309074</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24390,7 +24390,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="26">
@@ -24415,16 +24415,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>194.4189411335972</v>
       </c>
       <c r="H26" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I26" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24445,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>149.8691179411497</v>
@@ -24454,7 +24454,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>10.8230495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
         <v>251.3456529078365</v>
@@ -24463,13 +24463,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24488,10 +24488,10 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
         <v>137.3435171632106</v>
@@ -24536,13 +24536,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>65.38860888106225</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>247.1144340662031</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
@@ -24640,7 +24640,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H29" t="n">
-        <v>339.4748021157671</v>
+        <v>337.6653060427309</v>
       </c>
       <c r="I29" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24694,19 +24694,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>183.9558378705983</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="30">
@@ -24767,10 +24767,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>136.3170690290596</v>
+        <v>135.0341266295844</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -24779,13 +24779,13 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24810,7 +24810,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H31" t="n">
         <v>162.2271725074396</v>
@@ -24837,13 +24837,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S31" t="n">
         <v>224.0165980369723</v>
@@ -24874,7 +24874,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>382.7338416634806</v>
+        <v>330.3082731757329</v>
       </c>
       <c r="C32" t="n">
         <v>365.2728917710076</v>
@@ -24886,10 +24886,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24919,22 +24919,22 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>156.962040435181</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
@@ -24943,7 +24943,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="33">
@@ -25001,25 +25001,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>37.76413013191711</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>116.1075087528021</v>
       </c>
       <c r="Y33" t="n">
         <v>205.6826957773044</v>
@@ -25035,7 +25035,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C34" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D34" t="n">
         <v>148.6154730182124</v>
@@ -25089,7 +25089,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U34" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>141.7338416634806</v>
+        <v>180.4391552345834</v>
       </c>
       <c r="C35" t="n">
-        <v>124.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25126,10 +25126,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25171,7 +25171,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>115.4794584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
@@ -25180,7 +25180,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="36">
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>142.8603639960202</v>
+        <v>57.12999154646258</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25247,16 +25247,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -25323,7 +25323,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
         <v>286.3190293564909</v>
@@ -25332,7 +25332,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X37" t="n">
         <v>225.7096553890372</v>
@@ -25357,16 +25357,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>161.7172443298368</v>
       </c>
       <c r="F38" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
@@ -25393,7 +25393,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
@@ -25402,19 +25402,19 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>39.07285290783653</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V38" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
         <v>386.2379386560536</v>
@@ -25433,22 +25433,22 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>95.60874399080359</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25478,10 +25478,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>89.73620870693898</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>225.9413820809748</v>
@@ -25490,13 +25490,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25557,7 +25557,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
@@ -25572,7 +25572,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y40" t="n">
         <v>218.5846533520948</v>
@@ -25594,19 +25594,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>174.302737515135</v>
+        <v>363.5805828371576</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25630,25 +25630,25 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>146.9588679319578</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
@@ -25667,13 +25667,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>98.58069970823075</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
@@ -25712,28 +25712,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>150.1481968250288</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -25822,22 +25822,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C44" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D44" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E44" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F44" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H44" t="n">
         <v>339.4748021157671</v>
@@ -25876,7 +25876,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
         <v>251.3456529078365</v>
@@ -25885,13 +25885,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W44" t="n">
-        <v>349.240968717413</v>
+        <v>146.9462822885158</v>
       </c>
       <c r="X44" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y44" t="n">
-        <v>166.0516874347298</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="45">
@@ -25904,13 +25904,13 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>145.0692123933839</v>
@@ -25919,10 +25919,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0.7465913262578567</v>
@@ -25961,16 +25961,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V45" t="n">
-        <v>232.8005871494253</v>
+        <v>164.4231167504488</v>
       </c>
       <c r="W45" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X45" t="n">
-        <v>175.2629075727434</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="46">
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C46" t="n">
         <v>167.2468210986278</v>
@@ -26049,7 +26049,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y46" t="n">
-        <v>218.5846533520948</v>
+        <v>85.3976857667268</v>
       </c>
     </row>
   </sheetData>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674309</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674309</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>490164.0053302891</v>
+        <v>490173.9839674309</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>490164.0053302891</v>
+        <v>490173.9839674309</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>490164.0053302894</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>490164.0053302891</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>490164.0053302951</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674311</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>490164.0053302893</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>490164.0053302892</v>
+        <v>490173.9839674308</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>91386.50946835896</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="C2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223283</v>
       </c>
       <c r="D2" t="n">
-        <v>91386.50946835896</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="E2" t="n">
-        <v>91386.50946835901</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="F2" t="n">
-        <v>91386.50946835899</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="G2" t="n">
-        <v>91386.50946835903</v>
+        <v>91388.36989223286</v>
       </c>
       <c r="H2" t="n">
-        <v>91386.509468359</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="I2" t="n">
-        <v>91386.50946835899</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="J2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223283</v>
       </c>
       <c r="K2" t="n">
-        <v>91386.50946835901</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="L2" t="n">
-        <v>91386.50946836008</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="M2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223277</v>
       </c>
       <c r="N2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="O2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223283</v>
       </c>
       <c r="P2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223279</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="C4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="E4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="F4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="G4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>179.5221438966221</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="M4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="N4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="P4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-37838.05567553765</v>
+        <v>-37841.86290078054</v>
       </c>
       <c r="C6" t="n">
-        <v>42926.58732446237</v>
+        <v>42927.56863076719</v>
       </c>
       <c r="D6" t="n">
-        <v>42926.58732446235</v>
+        <v>42927.56863076718</v>
       </c>
       <c r="E6" t="n">
-        <v>76554.1873244624</v>
+        <v>76555.16863076718</v>
       </c>
       <c r="F6" t="n">
-        <v>76554.18732446237</v>
+        <v>76555.16863076718</v>
       </c>
       <c r="G6" t="n">
-        <v>76554.18732446241</v>
+        <v>76555.16863076722</v>
       </c>
       <c r="H6" t="n">
-        <v>76554.18732446239</v>
+        <v>76555.16863076718</v>
       </c>
       <c r="I6" t="n">
-        <v>76554.18732446237</v>
+        <v>76555.16863076716</v>
       </c>
       <c r="J6" t="n">
-        <v>13497.98332446236</v>
+        <v>13495.22603166096</v>
       </c>
       <c r="K6" t="n">
-        <v>76554.1873244624</v>
+        <v>76555.16863076715</v>
       </c>
       <c r="L6" t="n">
-        <v>76554.18732446345</v>
+        <v>76555.16863076715</v>
       </c>
       <c r="M6" t="n">
-        <v>76554.18732446236</v>
+        <v>76555.16863076713</v>
       </c>
       <c r="N6" t="n">
-        <v>76554.18732446236</v>
+        <v>76555.16863076718</v>
       </c>
       <c r="O6" t="n">
-        <v>76554.18732446236</v>
+        <v>76555.16863076719</v>
       </c>
       <c r="P6" t="n">
-        <v>76554.18732446236</v>
+        <v>76555.16863076715</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34614,7 +34614,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L2" t="n">
         <v>181.8947995804632</v>
@@ -34693,19 +34693,19 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>99.7689878253871</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="P3" t="n">
         <v>184.4883612256069</v>
@@ -34857,7 +34857,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M5" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N5" t="n">
         <v>207.9338608153932</v>
@@ -34930,25 +34930,25 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>104.6388282244066</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>241</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35094,7 +35094,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M8" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N8" t="n">
         <v>207.9338608153932</v>
@@ -35173,19 +35173,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O9" t="n">
-        <v>99.7689878253871</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P9" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35340,7 +35340,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P11" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,22 +35404,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L12" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P12" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35562,7 +35562,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L14" t="n">
         <v>181.8947995804632</v>
@@ -35647,19 +35647,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O15" t="n">
-        <v>99.7689878253871</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q15" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35805,7 +35805,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M17" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N17" t="n">
         <v>207.9338608153932</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L18" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M18" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N18" t="n">
-        <v>226.3927858636067</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P18" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q18" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36118,22 +36118,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
-        <v>161.1504669987997</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>184.4883612256069</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,19 +36352,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
-        <v>217.6787513871916</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>46.77426503701921</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>90.50913423401884</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37069,19 +37069,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37224,7 +37224,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
         <v>219.1673002655598</v>
@@ -37300,22 +37300,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>113.3528627008216</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37473,7 +37473,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37543,19 +37543,19 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>46.77426503701921</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,7 +37695,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
@@ -37774,22 +37774,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="O42" t="n">
-        <v>239.9766607390413</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37947,7 +37947,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P44" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38011,22 +38011,22 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L45" t="n">
-        <v>232.285965523585</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M45" t="n">
-        <v>239.9766607390412</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
